--- a/01_Input/00_CO Validation/Solomon Islands - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Solomon Islands - Energy Projects.xlsx
@@ -1,34 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26712"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27307"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wendy.wara\Documents\2023 RSD Folders\8. SOI CIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{7B22A26A-19AC-4DAA-864C-F52A33A2BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5AE1CF7-E84C-4B9C-A2A5-8F40040F915B}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{7B22A26A-19AC-4DAA-864C-F52A33A2BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ADBE4EA-82D3-4627-BACA-7656EFCD3763}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="4" r:id="rId1"/>
+    <sheet name="Projects" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_ftn1" localSheetId="1">Sheet1!$D$32</definedName>
-    <definedName name="_ftn2" localSheetId="1">Sheet1!$D$33</definedName>
-    <definedName name="_ftn3" localSheetId="1">Sheet1!$D$34</definedName>
-    <definedName name="_ftn4" localSheetId="1">Sheet1!$D$35</definedName>
-    <definedName name="_ftnref1" localSheetId="1">Sheet1!$G$16</definedName>
-    <definedName name="_ftnref2" localSheetId="1">Sheet1!$I$16</definedName>
-    <definedName name="_ftnref3" localSheetId="1">Sheet1!$G$18</definedName>
-    <definedName name="_ftnref4" localSheetId="1">Sheet1!$I$18</definedName>
+    <definedName name="_ftn1" localSheetId="2">Sheet1!$D$32</definedName>
+    <definedName name="_ftn2" localSheetId="2">Sheet1!$D$33</definedName>
+    <definedName name="_ftn3" localSheetId="2">Sheet1!$D$34</definedName>
+    <definedName name="_ftn4" localSheetId="2">Sheet1!$D$35</definedName>
+    <definedName name="_ftnref1" localSheetId="2">Sheet1!$G$16</definedName>
+    <definedName name="_ftnref2" localSheetId="2">Sheet1!$I$16</definedName>
+    <definedName name="_ftnref3" localSheetId="2">Sheet1!$G$18</definedName>
+    <definedName name="_ftnref4" localSheetId="2">Sheet1!$I$18</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -45,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
   <si>
     <t>Project ID</t>
   </si>
@@ -74,19 +78,37 @@
     <t>Donors</t>
   </si>
   <si>
-    <t xml:space="preserve">Comments </t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Year 4</t>
+    <t>Gender (% female)</t>
+  </si>
+  <si>
+    <t>VF or Non-VF</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>SEH Taxonomy</t>
+  </si>
+  <si>
+    <t>RISE Taxonomy</t>
+  </si>
+  <si>
+    <t>Flagship</t>
+  </si>
+  <si>
+    <t>Indirect Category</t>
+  </si>
+  <si>
+    <t>Indirect Taxonomy</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
   </si>
   <si>
     <t>SPIRES (Rural Electrification)</t>
@@ -98,19 +120,22 @@
     <t>Energy (MW added)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Project Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reduced annual growth rate of Green House Gas (GHG) emissions in the energy and energy end use sector of the country.</t>
-    </r>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Some Sources</t>
+  </si>
+  <si>
+    <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <r>
@@ -129,6 +154,57 @@
     </r>
   </si>
   <si>
+    <t>Number of beneficiaries</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. of new jobs created due to enhanced electricity access in off-grid areas in the country </t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>No. of trained national and local government personnel that can ably plan and evaluate energy access, sustainable energy and low carbon technology application projects.</t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>No. of local firms that can capably provide technical, engineering and maintenance services for rural electrification and low carbon technology application projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments </t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Project Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reduced annual growth rate of Green House Gas (GHG) emissions in the energy and energy end use sector of the country.</t>
+    </r>
+  </si>
+  <si>
     <t>Note to CO: Although the details you provide are very thorough, it would be more helpful if you could provide less information such that it fits into our categorizations. For access to electricity we need this reported either as a number of beneficiaries or a number of MW. For services (health, water) these need to be distilled also into an estimate of nubmers of beneficiaries, unless this is a policy-level or strategic output that doesn't translate directly into beneficiaries, and then you can tag is as a Policy or Regulatory Framework. For the targets, we are primarily concerned with the total expected output of this project, so please provide only a single value for the target and baseline based on the beginning and end of the project.</t>
   </si>
   <si>
@@ -160,9 +236,6 @@
   </si>
   <si>
     <t>% electricity access in rural areas, %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. of new jobs created due to enhanced electricity access in off-grid areas in the country </t>
   </si>
   <si>
     <r>
@@ -331,9 +404,6 @@
   </si>
   <si>
     <t>100% Ministry of Mines and Energy with no external support</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
   </si>
   <si>
     <r>
@@ -406,12 +476,6 @@
     </r>
   </si>
   <si>
-    <t>No. of trained national and local government personnel that can ably plan and evaluate energy access, sustainable energy and low carbon technology application projects.</t>
-  </si>
-  <si>
-    <t>No. of local firms that can capably provide technical, engineering and maintenance services for rural electrification and low carbon technology application projects</t>
-  </si>
-  <si>
     <t>[1] Enhancement in carrying out energy service fee collection in community demo site.</t>
   </si>
   <si>
@@ -479,46 +543,58 @@
     <t xml:space="preserve">Percentage of women in community-based Renewable Energy Service Companies (RESCO) morally supported by village men to build their confidence in leadership </t>
   </si>
   <si>
-    <t>Tier</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Access to Energy</t>
-  </si>
-  <si>
-    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
-  </si>
-  <si>
-    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
+    <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
+  </si>
+  <si>
+    <t>Number of MW installed capacity</t>
   </si>
   <si>
     <t>Clean Cooking</t>
   </si>
   <si>
-    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
-  </si>
-  <si>
-    <t>Productive Use of Energy</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>Access to agricultural energy services (irrigation with solar pumps, heating systems for processing food, etc. )</t>
-  </si>
-  <si>
-    <t>Access to health services powered by solar PV and energy efficient systems such as hospitals</t>
-  </si>
-  <si>
-    <t>Access to solar water pumps</t>
+    <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
+  </si>
+  <si>
+    <t>Clean Heating</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
+  </si>
+  <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean, affordable, and sustainable electricity for agricultural and food system activities (direct access to power machines for crop, processing, milling, grinding, de-husking, pressing, canning, sealing and packaging electricity, heating, cooling, solar water pumping for irrigation etc.) </t>
+  </si>
+  <si>
+    <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
+  </si>
+  <si>
+    <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
   </si>
   <si>
     <t>Education Services</t>
   </si>
   <si>
-    <t>Access to education services trough clean energy systems</t>
+    <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -527,7 +603,10 @@
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
   </si>
   <si>
-    <t>Market Development</t>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support for the development of market ecosystem </t>
   </si>
   <si>
     <t>Medium Enterprises</t>
@@ -536,19 +615,10 @@
     <t>Support for the development of medium enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
     <t>Support for the development of small enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Capacity Building</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t>Individuals who participate in trainings for energy activities</t>
+    <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
   </si>
   <si>
     <t>Entrepreneurship Training</t>
@@ -557,19 +627,19 @@
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
   </si>
   <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
+  </si>
+  <si>
     <t>Campaign Participant</t>
   </si>
   <si>
     <t>Individuals who participate in advocacy and campaign on energy</t>
   </si>
   <si>
-    <t>Policy and Regulator Frameworks</t>
-  </si>
-  <si>
-    <t>Policies and regulatory framework can have far-reaching impacts on the energy access situation in countries</t>
-  </si>
-  <si>
-    <t>Other</t>
+    <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
   </si>
   <si>
     <t>Any other type of beneficiary (please specify justification in Notes)</t>
@@ -582,12 +652,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -672,8 +748,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -688,42 +777,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAFFFFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FFFFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42FFFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00E1DA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00DAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00BDB7"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -750,32 +809,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -783,17 +816,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1001,64 +1023,140 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1067,49 +1165,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1121,113 +1312,101 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1235,7 +1414,103 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFD966"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF9BC2E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1636,6 +1911,383 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC04F94-F9A8-49FC-B047-3D156302B7DD}">
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="126" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="30.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="45.75">
+      <c r="A2" s="28">
+        <v>6089</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="29">
+        <v>2639726</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="47">
+        <v>0</v>
+      </c>
+      <c r="H2" s="48">
+        <f>((5*15)+(2*30)+(7*13)+(5*30)+(5*10)+(2*30)+(2*15)+(2*50)+26+30+(2*15)+75+25+(3*75)+(2*25)+(16*1.5)+(16*12.5)+2000)/1000</f>
+        <v>3.3010000000000002</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="39"/>
+      <c r="K2" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="49"/>
+      <c r="M2" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="49"/>
+      <c r="T2" s="58"/>
+    </row>
+    <row r="3" spans="1:20" ht="45.75">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="17">
+        <v>0</v>
+      </c>
+      <c r="H3" s="35">
+        <v>19147</v>
+      </c>
+      <c r="I3" s="33"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="49"/>
+      <c r="M3" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="58"/>
+    </row>
+    <row r="4" spans="1:20" ht="45.75">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="44"/>
+      <c r="H4" s="59">
+        <f>0.8*0.25*615804</f>
+        <v>123160.8</v>
+      </c>
+      <c r="I4" s="31"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="49"/>
+      <c r="M4" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="58"/>
+    </row>
+    <row r="5" spans="1:20" ht="52.5" customHeight="1">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="17">
+        <v>10</v>
+      </c>
+      <c r="H5" s="36">
+        <v>200</v>
+      </c>
+      <c r="I5" s="31"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="49"/>
+      <c r="M5" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="58"/>
+    </row>
+    <row r="6" spans="1:20" ht="45.75">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37">
+        <v>4</v>
+      </c>
+      <c r="I6" s="31"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="49"/>
+      <c r="M6" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="58"/>
+    </row>
+    <row r="7" spans="1:20" ht="45.75">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="37">
+        <v>3</v>
+      </c>
+      <c r="I7" s="31"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="49"/>
+      <c r="M7" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="58"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="58"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="G9" s="14"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="J3:J7">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+      <formula>"Missing"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+      <formula>"New"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="CO Update">
+      <formula>NOT(ISERROR(SEARCH("CO Update",J3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J7">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+      <formula>"Not Updated"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+      <formula>"Assumed no projects"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+      <formula>"Review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"Updated"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+      <formula>"Missing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P7" xr:uid="{44170BD7-949B-4F5E-A591-2D6F21FD59F8}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O7" xr:uid="{BCFDB5E4-ACC3-4A0E-B883-1C5312DE5C70}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M7" xr:uid="{CEBB5F99-5834-4327-BEE4-0221F4A205E6}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N7" xr:uid="{77A6029E-0BCB-4200-BA0B-288B95290BC6}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L7" xr:uid="{7CA57EBB-B3BB-4CB0-AB3F-260C0B0FC95F}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S7" xr:uid="{6D089871-D030-4194-B15B-61E7C5915D77}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K7" xr:uid="{54B635D1-7EC0-4A23-9A5B-349138102771}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q7" xr:uid="{62F8D9DE-743D-424D-8D18-B5D0A06F7197}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R7" xr:uid="{FCB354B3-B571-4D2C-9AA7-62EA19D7B6D6}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{42A6F645-823C-4D07-8701-D13A558507DF}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
@@ -1668,683 +2320,674 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="30.75">
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1">
+      <c r="A3" s="69">
+        <v>6089</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="70">
+        <v>2639726</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+    </row>
+    <row r="4" spans="1:14" ht="184.5" customHeight="1">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0</v>
+      </c>
+      <c r="H4" s="17">
+        <v>0</v>
+      </c>
+      <c r="I4" s="18">
+        <v>6376</v>
+      </c>
+      <c r="J4" s="18">
+        <v>12771</v>
+      </c>
+      <c r="K4" s="18">
+        <v>19147</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="39.6" customHeight="1">
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="17">
+        <v>6.42</v>
+      </c>
+      <c r="H5" s="17">
+        <v>6.3</v>
+      </c>
+      <c r="I5" s="17">
+        <v>6.2</v>
+      </c>
+      <c r="J5" s="17">
+        <v>6.05</v>
+      </c>
+      <c r="K5" s="17">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1">
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+    </row>
+    <row r="7" spans="1:14" ht="65.45" customHeight="1">
+      <c r="A7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17">
+        <v>697.6</v>
+      </c>
+      <c r="J7" s="19">
+        <v>1397.3</v>
+      </c>
+      <c r="K7" s="19">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A8" s="69"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="J8" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="K8" s="20">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="52.5" customHeight="1">
+      <c r="A9" s="69"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="17">
+        <v>10</v>
+      </c>
+      <c r="H9" s="17">
+        <v>20</v>
+      </c>
+      <c r="I9" s="17">
+        <v>60</v>
+      </c>
+      <c r="J9" s="17">
+        <v>100</v>
+      </c>
+      <c r="K9" s="17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="69"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
+        <v>1</v>
+      </c>
+      <c r="I11" s="15">
+        <v>2</v>
+      </c>
+      <c r="J11" s="15">
+        <v>3</v>
+      </c>
+      <c r="K11" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="69"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15">
+        <v>1</v>
+      </c>
+      <c r="J12" s="15">
+        <v>2</v>
+      </c>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" ht="52.5" customHeight="1">
+      <c r="A13" s="69"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15">
+        <v>5</v>
+      </c>
+      <c r="H13" s="15">
+        <v>6</v>
+      </c>
+      <c r="I13" s="15">
+        <v>7</v>
+      </c>
+      <c r="J13" s="15">
+        <v>8</v>
+      </c>
+      <c r="K13" s="15">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30.75">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1">
-      <c r="A3" s="41">
-        <v>6089</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="42">
-        <v>2639726</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-    </row>
-    <row r="4" spans="1:14" ht="184.5" customHeight="1">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="30" t="s">
+    <row r="14" spans="1:14">
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="63">
+        <v>0</v>
+      </c>
+      <c r="H16" s="63"/>
+      <c r="I16" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="63"/>
+      <c r="K16" s="64" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="69"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="64"/>
+    </row>
+    <row r="18" spans="1:11" ht="65.45" customHeight="1">
+      <c r="A18" s="69"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="69"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+    </row>
+    <row r="20" spans="1:11" ht="26.1">
+      <c r="A20" s="69"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="15">
+        <v>0</v>
+      </c>
+      <c r="H20" s="15">
+        <v>1</v>
+      </c>
+      <c r="I20" s="15">
+        <v>2</v>
+      </c>
+      <c r="J20" s="15">
+        <v>4</v>
+      </c>
+      <c r="K20" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="26.1">
+      <c r="A21" s="69"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15">
+        <v>2</v>
+      </c>
+      <c r="I21" s="15">
+        <v>4</v>
+      </c>
+      <c r="J21" s="15">
+        <v>5</v>
+      </c>
+      <c r="K21" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="104.1">
+      <c r="A22" s="69"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="69"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="24">
+      <c r="F23" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+    </row>
+    <row r="24" spans="1:11" ht="26.1">
+      <c r="A24" s="69"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="15">
         <v>0</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H24" s="15">
+        <v>1</v>
+      </c>
+      <c r="I24" s="15">
+        <v>2</v>
+      </c>
+      <c r="J24" s="15">
+        <v>4</v>
+      </c>
+      <c r="K24" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="26.1">
+      <c r="A25" s="69"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="15">
         <v>0</v>
       </c>
-      <c r="I4" s="25">
-        <v>6376</v>
-      </c>
-      <c r="J4" s="25">
-        <v>12771</v>
-      </c>
-      <c r="K4" s="25">
-        <v>19147</v>
-      </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="39.6" customHeight="1">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="24">
-        <v>6.42</v>
-      </c>
-      <c r="H5" s="24">
-        <v>6.3</v>
-      </c>
-      <c r="I5" s="24">
-        <v>6.2</v>
-      </c>
-      <c r="J5" s="24">
-        <v>6.05</v>
-      </c>
-      <c r="K5" s="24">
-        <v>5.87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-    </row>
-    <row r="7" spans="1:14" ht="65.45" customHeight="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="24">
+      <c r="H25" s="15">
+        <v>2</v>
+      </c>
+      <c r="I25" s="15">
+        <v>4</v>
+      </c>
+      <c r="J25" s="15">
+        <v>6</v>
+      </c>
+      <c r="K25" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="26.1">
+      <c r="A26" s="69"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="15">
         <v>0</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H26" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="I26" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="J26" s="21">
+        <v>0.35</v>
+      </c>
+      <c r="K26" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="69"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+    </row>
+    <row r="28" spans="1:11" ht="26.1">
+      <c r="A28" s="69"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="15">
         <v>0</v>
       </c>
-      <c r="I7" s="24">
-        <v>697.6</v>
-      </c>
-      <c r="J7" s="26">
-        <v>1397.3</v>
-      </c>
-      <c r="K7" s="26">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="26.45" customHeight="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="27">
-        <v>0.05</v>
-      </c>
-      <c r="H8" s="27">
-        <v>0.1</v>
-      </c>
-      <c r="I8" s="27">
-        <v>0.15</v>
-      </c>
-      <c r="J8" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="K8" s="27">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="52.5" customHeight="1">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="24">
-        <v>10</v>
-      </c>
-      <c r="H9" s="24">
-        <v>20</v>
-      </c>
-      <c r="I9" s="24">
-        <v>60</v>
-      </c>
-      <c r="J9" s="24">
-        <v>100</v>
-      </c>
-      <c r="K9" s="24">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="22">
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="H11" s="22">
+      <c r="I28" s="15">
+        <v>2</v>
+      </c>
+      <c r="J28" s="15">
+        <v>3</v>
+      </c>
+      <c r="K28" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="26.1">
+      <c r="A29" s="69"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" s="15">
         <v>1</v>
       </c>
-      <c r="I11" s="22">
+      <c r="H29" s="15">
+        <v>1</v>
+      </c>
+      <c r="I29" s="15">
+        <v>1</v>
+      </c>
+      <c r="J29" s="15">
         <v>2</v>
       </c>
-      <c r="J11" s="22">
+      <c r="K29" s="15">
         <v>3</v>
       </c>
-      <c r="K11" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="22">
-        <v>0</v>
-      </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22">
-        <v>1</v>
-      </c>
-      <c r="J12" s="22">
-        <v>2</v>
-      </c>
-      <c r="K12" s="22"/>
-    </row>
-    <row r="13" spans="1:14" ht="52.5" customHeight="1">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="22">
-        <v>5</v>
-      </c>
-      <c r="H13" s="22">
-        <v>6</v>
-      </c>
-      <c r="I13" s="22">
-        <v>7</v>
-      </c>
-      <c r="J13" s="22">
-        <v>8</v>
-      </c>
-      <c r="K13" s="22">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="48">
-        <v>0</v>
-      </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="48"/>
-      <c r="K16" s="49" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="41"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="49"/>
-    </row>
-    <row r="18" spans="1:11" ht="65.45" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="22">
-        <v>0</v>
-      </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-    </row>
-    <row r="20" spans="1:11" ht="26.1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="22">
-        <v>0</v>
-      </c>
-      <c r="H20" s="22">
-        <v>1</v>
-      </c>
-      <c r="I20" s="22">
-        <v>2</v>
-      </c>
-      <c r="J20" s="22">
-        <v>4</v>
-      </c>
-      <c r="K20" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="26.1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="22">
-        <v>0</v>
-      </c>
-      <c r="H21" s="22">
-        <v>2</v>
-      </c>
-      <c r="I21" s="22">
-        <v>4</v>
-      </c>
-      <c r="J21" s="22">
-        <v>5</v>
-      </c>
-      <c r="K21" s="22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="104.1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="22">
-        <v>0</v>
-      </c>
-      <c r="H22" s="28">
-        <v>0.25</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22" s="28">
-        <v>0.75</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-    </row>
-    <row r="24" spans="1:11" ht="26.1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="22">
-        <v>0</v>
-      </c>
-      <c r="H24" s="22">
-        <v>1</v>
-      </c>
-      <c r="I24" s="22">
-        <v>2</v>
-      </c>
-      <c r="J24" s="22">
-        <v>4</v>
-      </c>
-      <c r="K24" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="26.1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="22">
-        <v>0</v>
-      </c>
-      <c r="H25" s="22">
-        <v>2</v>
-      </c>
-      <c r="I25" s="22">
-        <v>4</v>
-      </c>
-      <c r="J25" s="22">
-        <v>6</v>
-      </c>
-      <c r="K25" s="22">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="26.1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" s="22">
-        <v>0</v>
-      </c>
-      <c r="H26" s="28">
-        <v>0.1</v>
-      </c>
-      <c r="I26" s="28">
-        <v>0.25</v>
-      </c>
-      <c r="J26" s="28">
-        <v>0.35</v>
-      </c>
-      <c r="K26" s="28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-    </row>
-    <row r="28" spans="1:11" ht="26.1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="22">
-        <v>0</v>
-      </c>
-      <c r="H28" s="22">
-        <v>0</v>
-      </c>
-      <c r="I28" s="22">
-        <v>2</v>
-      </c>
-      <c r="J28" s="22">
-        <v>3</v>
-      </c>
-      <c r="K28" s="22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="26.1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="22">
-        <v>1</v>
-      </c>
-      <c r="H29" s="22">
-        <v>1</v>
-      </c>
-      <c r="I29" s="22">
-        <v>1</v>
-      </c>
-      <c r="J29" s="22">
-        <v>2</v>
-      </c>
-      <c r="K29" s="22">
-        <v>3</v>
-      </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="G30" s="21"/>
+      <c r="G30" s="14"/>
     </row>
     <row r="31" spans="1:11" ht="26.25" customHeight="1">
-      <c r="F31" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="21"/>
+      <c r="F31" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="F32" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="21"/>
+      <c r="F32" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="6:7">
-      <c r="F33" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G33" s="21"/>
+      <c r="F33" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="6:7">
-      <c r="F34" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="21"/>
+      <c r="F34" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="6:7">
-      <c r="G35" s="21"/>
+      <c r="G35" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F27:K27"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="F3:K3"/>
     <mergeCell ref="F6:K6"/>
@@ -2361,6 +3004,15 @@
     <mergeCell ref="E18:E22"/>
     <mergeCell ref="E23:E29"/>
     <mergeCell ref="F15:K15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="F27:K27"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
@@ -2400,7 +3052,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E3</xm:sqref>
         </x14:dataValidation>
@@ -2410,499 +3062,499 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E139CA92-2C16-454F-A4E4-09819066132A}">
   <dimension ref="D1:I35"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="4" max="4" width="120.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:9" ht="15" thickBot="1">
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="57"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="82"/>
     </row>
     <row r="2" spans="4:9" ht="15" thickBot="1">
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="4:9" ht="27.6" customHeight="1" thickBot="1">
+      <c r="D3" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="79"/>
+    </row>
+    <row r="4" spans="4:9" ht="15.6" thickBot="1">
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>6376</v>
+      </c>
+      <c r="H4" s="7">
+        <v>12771</v>
+      </c>
+      <c r="I4" s="7">
+        <v>19147</v>
+      </c>
+    </row>
+    <row r="5" spans="4:9" ht="15" thickBot="1">
+      <c r="D5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="6">
+        <v>6.42</v>
+      </c>
+      <c r="F5" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>6.05</v>
+      </c>
+      <c r="I5" s="6">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="6" spans="4:9" ht="26.1" customHeight="1" thickBot="1">
+      <c r="D6" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="85"/>
+    </row>
+    <row r="7" spans="4:9" ht="15" thickBot="1">
+      <c r="D7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>697.6</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1397.3</v>
+      </c>
+      <c r="I7" s="8">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="8" spans="4:9" ht="15" thickBot="1">
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="4:9" ht="15" thickBot="1">
+      <c r="D9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="6">
         <v>10</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="4:9" ht="27.6" customHeight="1" thickBot="1">
-      <c r="D3" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54"/>
-    </row>
-    <row r="4" spans="4:9" ht="15.6" thickBot="1">
-      <c r="D4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="13">
+      <c r="F9" s="6">
+        <v>20</v>
+      </c>
+      <c r="G9" s="6">
+        <v>60</v>
+      </c>
+      <c r="H9" s="6">
+        <v>100</v>
+      </c>
+      <c r="I9" s="6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="4:9" ht="15" thickBot="1">
+      <c r="D10" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="79"/>
+    </row>
+    <row r="11" spans="4:9" ht="15" thickBot="1">
+      <c r="D11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="5">
         <v>0</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="4:9" ht="15" thickBot="1">
+      <c r="D12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="5">
         <v>0</v>
       </c>
-      <c r="G4" s="14">
-        <v>6376</v>
-      </c>
-      <c r="H4" s="14">
-        <v>12771</v>
-      </c>
-      <c r="I4" s="14">
-        <v>19147</v>
-      </c>
-    </row>
-    <row r="5" spans="4:9" ht="15" thickBot="1">
-      <c r="D5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="13">
-        <v>6.42</v>
-      </c>
-      <c r="F5" s="13">
-        <v>6.3</v>
-      </c>
-      <c r="G5" s="13">
-        <v>6.2</v>
-      </c>
-      <c r="H5" s="13">
-        <v>6.05</v>
-      </c>
-      <c r="I5" s="13">
-        <v>5.87</v>
-      </c>
-    </row>
-    <row r="6" spans="4:9" ht="26.1" customHeight="1" thickBot="1">
-      <c r="D6" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="60"/>
-    </row>
-    <row r="7" spans="4:9" ht="15" thickBot="1">
-      <c r="D7" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="4:9" ht="15" thickBot="1">
+      <c r="D13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5">
+        <v>7</v>
+      </c>
+      <c r="H13" s="5">
+        <v>8</v>
+      </c>
+      <c r="I13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="4:9">
+      <c r="D14" s="86" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="88"/>
+    </row>
+    <row r="15" spans="4:9" ht="15" thickBot="1">
+      <c r="D15" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
+    </row>
+    <row r="16" spans="4:9">
+      <c r="D16" s="92" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="94">
         <v>0</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F16" s="96"/>
+      <c r="G16" s="98" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="96"/>
+      <c r="I16" s="75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="4:9" ht="15" thickBot="1">
+      <c r="D17" s="93"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="76"/>
+    </row>
+    <row r="18" spans="4:9" ht="15" thickBot="1">
+      <c r="D18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="5">
         <v>0</v>
       </c>
-      <c r="G7" s="13">
-        <v>697.6</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1397.3</v>
-      </c>
-      <c r="I7" s="15">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="8" spans="4:9" ht="15" thickBot="1">
-      <c r="D8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="17">
-        <v>0.05</v>
-      </c>
-      <c r="F8" s="17">
+      <c r="F18" s="5"/>
+      <c r="G18" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="4:9" ht="40.5" customHeight="1" thickBot="1">
+      <c r="D19" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+    </row>
+    <row r="20" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5">
+        <v>4</v>
+      </c>
+      <c r="I20" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5">
+        <v>4</v>
+      </c>
+      <c r="H21" s="5">
+        <v>5</v>
+      </c>
+      <c r="I21" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="4:9" ht="67.5">
+      <c r="D22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" ht="40.5" customHeight="1" thickBot="1">
+      <c r="D23" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="79"/>
+    </row>
+    <row r="24" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5">
+        <v>4</v>
+      </c>
+      <c r="I24" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5">
+        <v>4</v>
+      </c>
+      <c r="H25" s="5">
+        <v>6</v>
+      </c>
+      <c r="I25" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D26" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
         <v>0.1</v>
       </c>
-      <c r="G8" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="H8" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="I8" s="17">
+      <c r="G26" s="9">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="9" spans="4:9" ht="15" thickBot="1">
-      <c r="D9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="13">
-        <v>10</v>
-      </c>
-      <c r="F9" s="13">
-        <v>20</v>
-      </c>
-      <c r="G9" s="13">
-        <v>60</v>
-      </c>
-      <c r="H9" s="13">
-        <v>100</v>
-      </c>
-      <c r="I9" s="13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="4:9" ht="15" thickBot="1">
-      <c r="D10" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="54"/>
-    </row>
-    <row r="11" spans="4:9" ht="15" thickBot="1">
-      <c r="D11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="H26" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="4:9" ht="15" thickBot="1">
+      <c r="D27" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="79"/>
+    </row>
+    <row r="28" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="5">
         <v>0</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F28" s="5">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5">
+        <v>3</v>
+      </c>
+      <c r="I28" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="4:9" ht="26.45" thickBot="1">
+      <c r="D29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="5">
         <v>1</v>
       </c>
-      <c r="G11" s="12">
+      <c r="F29" s="5">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5">
         <v>2</v>
       </c>
-      <c r="H11" s="12">
+      <c r="I29" s="5">
         <v>3</v>
       </c>
-      <c r="I11" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="4:9" ht="15" thickBot="1">
-      <c r="D12" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="12">
-        <v>2</v>
-      </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="4:9" ht="15" thickBot="1">
-      <c r="D13" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="12">
-        <v>5</v>
-      </c>
-      <c r="F13" s="12">
-        <v>6</v>
-      </c>
-      <c r="G13" s="12">
-        <v>7</v>
-      </c>
-      <c r="H13" s="12">
-        <v>8</v>
-      </c>
-      <c r="I13" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="4:9">
-      <c r="D14" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="63"/>
-    </row>
-    <row r="15" spans="4:9" ht="15" thickBot="1">
-      <c r="D15" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="66"/>
-    </row>
-    <row r="16" spans="4:9">
-      <c r="D16" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="69">
-        <v>0</v>
-      </c>
-      <c r="F16" s="71"/>
-      <c r="G16" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="71"/>
-      <c r="I16" s="50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="4:9" ht="15" thickBot="1">
-      <c r="D17" s="68"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="51"/>
-    </row>
-    <row r="18" spans="4:9" ht="15" thickBot="1">
-      <c r="D18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="12">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="4:9" ht="40.5" customHeight="1" thickBot="1">
-      <c r="D19" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="54"/>
-    </row>
-    <row r="20" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="12">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12">
-        <v>1</v>
-      </c>
-      <c r="G20" s="12">
-        <v>2</v>
-      </c>
-      <c r="H20" s="12">
-        <v>4</v>
-      </c>
-      <c r="I20" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0</v>
-      </c>
-      <c r="F21" s="12">
-        <v>2</v>
-      </c>
-      <c r="G21" s="12">
-        <v>4</v>
-      </c>
-      <c r="H21" s="12">
-        <v>5</v>
-      </c>
-      <c r="I21" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="4:9" ht="67.5">
-      <c r="D22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="12">
-        <v>0</v>
-      </c>
-      <c r="F22" s="16">
-        <v>0.25</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="16">
-        <v>0.75</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="4:9" ht="40.5" customHeight="1" thickBot="1">
-      <c r="D23" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="54"/>
-    </row>
-    <row r="24" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D24" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="12">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12">
-        <v>1</v>
-      </c>
-      <c r="G24" s="12">
-        <v>2</v>
-      </c>
-      <c r="H24" s="12">
-        <v>4</v>
-      </c>
-      <c r="I24" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D25" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="12">
-        <v>0</v>
-      </c>
-      <c r="F25" s="12">
-        <v>2</v>
-      </c>
-      <c r="G25" s="12">
-        <v>4</v>
-      </c>
-      <c r="H25" s="12">
-        <v>6</v>
-      </c>
-      <c r="I25" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D26" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="12">
-        <v>0</v>
-      </c>
-      <c r="F26" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="G26" s="16">
-        <v>0.25</v>
-      </c>
-      <c r="H26" s="16">
-        <v>0.35</v>
-      </c>
-      <c r="I26" s="16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="4:9" ht="15" thickBot="1">
-      <c r="D27" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="54"/>
-    </row>
-    <row r="28" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D28" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="12">
-        <v>0</v>
-      </c>
-      <c r="F28" s="12">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12">
-        <v>2</v>
-      </c>
-      <c r="H28" s="12">
-        <v>3</v>
-      </c>
-      <c r="I28" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="4:9" ht="26.45" thickBot="1">
-      <c r="D29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="12">
-        <v>1</v>
-      </c>
-      <c r="F29" s="12">
-        <v>1</v>
-      </c>
-      <c r="G29" s="12">
-        <v>1</v>
-      </c>
-      <c r="H29" s="12">
-        <v>2</v>
-      </c>
-      <c r="I29" s="12">
-        <v>3</v>
-      </c>
     </row>
     <row r="32" spans="4:9">
-      <c r="D32" s="20" t="s">
-        <v>55</v>
+      <c r="D32" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="4:4">
-      <c r="D33" s="20" t="s">
-        <v>56</v>
+      <c r="D33" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="4:4">
-      <c r="D34" s="20" t="s">
-        <v>57</v>
+      <c r="D34" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="4:4">
-      <c r="D35" s="20" t="s">
-        <v>58</v>
+      <c r="D35" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2937,185 +3589,217 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="52.7109375" customWidth="1"/>
-    <col min="3" max="3" width="95.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="95.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="75"/>
-      <c r="B3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="75"/>
-      <c r="B4" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="76"/>
-      <c r="B6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="76"/>
-      <c r="B7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="76"/>
-      <c r="B8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="76"/>
-      <c r="B9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="77"/>
-      <c r="B11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B1" s="50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30.75">
+      <c r="A2" s="100" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="51" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="78" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="6" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B4" s="51" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="78"/>
-      <c r="B13" s="7" t="s">
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B5" s="51" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="78"/>
-      <c r="B14" s="8" t="s">
+    <row r="6" spans="1:2" ht="60.75">
+      <c r="A6" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B6" s="51" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
+    <row r="7" spans="1:2" ht="30.75">
+      <c r="A7" s="100" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="30.75">
+      <c r="A8" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="51" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
+    <row r="9" spans="1:2" ht="30.75">
+      <c r="A9" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B9" s="51" t="s">
         <v>100</v>
       </c>
     </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="101" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="100" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="101" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30.75">
+      <c r="A12" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="100" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="101" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="101" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="100" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="101" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="100" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="100" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="101" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="45.75">
+      <c r="A19" s="100" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="101" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="101" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30.75">
+      <c r="A21" s="100" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="102" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="101" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3364,28 +4048,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFF3D39-54DD-416F-A50A-C635A1FF38F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8739B117-156A-40FE-B2D5-DD22F5B6A59B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3393,5 +4057,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8739B117-156A-40FE-B2D5-DD22F5B6A59B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFF3D39-54DD-416F-A50A-C635A1FF38F2}"/>
 </file>
--- a/01_Input/00_CO Validation/Solomon Islands - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Solomon Islands - Energy Projects.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27307"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wendy.wara\Documents\2023 RSD Folders\8. SOI CIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{7B22A26A-19AC-4DAA-864C-F52A33A2BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ADBE4EA-82D3-4627-BACA-7656EFCD3763}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{7B22A26A-19AC-4DAA-864C-F52A33A2BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D0F05E0-2F7D-4529-9318-ED06613CD4F1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (2)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects" sheetId="1" r:id="rId2"/>
+    <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="124">
   <si>
     <t>Project ID</t>
   </si>
@@ -136,6 +136,78 @@
   </si>
   <si>
     <t>GHG Emissions Reduction</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cumulative Incremental GHG emission reduction from the electricity sector in rural areas, Millions of tons CO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>Number of beneficiaries</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. of new jobs created due to enhanced electricity access in off-grid areas in the country </t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>No. of trained national and local government personnel that can ably plan and evaluate energy access, sustainable energy and low carbon technology application projects.</t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>No. of local firms that can capably provide technical, engineering and maintenance services for rural electrification and low carbon technology application projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments </t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Project Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reduced annual growth rate of Green House Gas (GHG) emissions in the energy and energy end use sector of the country.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -151,57 +223,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>Number of beneficiaries</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. of new jobs created due to enhanced electricity access in off-grid areas in the country </t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t>No. of trained national and local government personnel that can ably plan and evaluate energy access, sustainable energy and low carbon technology application projects.</t>
-  </si>
-  <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
-    <t>No. of local firms that can capably provide technical, engineering and maintenance services for rural electrification and low carbon technology application projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments </t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Year 4</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Project Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reduced annual growth rate of Green House Gas (GHG) emissions in the energy and energy end use sector of the country.</t>
     </r>
   </si>
   <si>
@@ -649,10 +670,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,6 +779,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -1118,7 +1153,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1210,9 +1245,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1279,51 +1311,51 @@
     <xf numFmtId="1" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1399,6 +1431,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1410,8 +1448,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
@@ -1919,8 +1957,8 @@
     <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="126" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1955,37 +1993,37 @@
       <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="52" t="s">
+      <c r="K1" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53" t="s">
+      <c r="L1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="52" t="s">
+      <c r="M1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="53" t="s">
+      <c r="O1" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="53" t="s">
+      <c r="P1" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="54" t="s">
+      <c r="Q1" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="55" t="s">
+      <c r="R1" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="S1" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="55" t="s">
+      <c r="T1" s="54" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2002,104 +2040,104 @@
       <c r="D2" s="29">
         <v>2639726</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="47">
+      <c r="G2" s="46">
         <v>0</v>
       </c>
-      <c r="H2" s="48">
+      <c r="H2" s="47">
         <f>((5*15)+(2*30)+(7*13)+(5*30)+(5*10)+(2*30)+(2*15)+(2*50)+26+30+(2*15)+75+25+(3*75)+(2*25)+(16*1.5)+(16*12.5)+2000)/1000</f>
         <v>3.3010000000000002</v>
       </c>
       <c r="I2" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="38"/>
+      <c r="K2" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="57" t="s">
+      <c r="L2" s="48"/>
+      <c r="M2" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="58" t="s">
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="49"/>
-      <c r="T2" s="58"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="57"/>
     </row>
     <row r="3" spans="1:20" ht="45.75">
       <c r="A3" s="28"/>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="40" t="s">
+      <c r="D3" s="40"/>
+      <c r="E3" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="100" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="17">
         <v>0</v>
       </c>
-      <c r="H3" s="35">
-        <v>19147</v>
+      <c r="H3" s="99">
+        <v>1.9147000000000001E-2</v>
       </c>
       <c r="I3" s="33"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="56" t="s">
+      <c r="J3" s="38"/>
+      <c r="K3" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="49"/>
-      <c r="M3" s="57" t="s">
+      <c r="L3" s="48"/>
+      <c r="M3" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="58"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="57"/>
     </row>
     <row r="4" spans="1:20" ht="45.75">
       <c r="A4" s="28"/>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="29"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="43" t="s">
+      <c r="E4" s="41"/>
+      <c r="F4" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="44"/>
-      <c r="H4" s="59">
+      <c r="G4" s="43"/>
+      <c r="H4" s="58">
         <f>0.8*0.25*615804</f>
         <v>123160.8</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="56" t="s">
+      <c r="J4" s="38"/>
+      <c r="K4" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="49"/>
-      <c r="M4" s="57" t="s">
+      <c r="L4" s="48"/>
+      <c r="M4" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="58"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="57"/>
     </row>
     <row r="5" spans="1:20" ht="52.5" customHeight="1">
       <c r="A5" s="28"/>
@@ -2115,27 +2153,27 @@
       <c r="G5" s="17">
         <v>10</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="35">
         <v>200</v>
       </c>
       <c r="I5" s="31"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="56" t="s">
+      <c r="J5" s="38"/>
+      <c r="K5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="49"/>
-      <c r="M5" s="57" t="s">
+      <c r="L5" s="48"/>
+      <c r="M5" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="58"/>
-    </row>
-    <row r="6" spans="1:20" ht="45.75">
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="57"/>
+    </row>
+    <row r="6" spans="1:20" ht="56.25" customHeight="1">
       <c r="A6" s="28"/>
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
@@ -2149,27 +2187,27 @@
       <c r="G6" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="36">
         <v>4</v>
       </c>
       <c r="I6" s="31"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="56" t="s">
+      <c r="J6" s="38"/>
+      <c r="K6" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="49"/>
-      <c r="M6" s="57" t="s">
+      <c r="L6" s="48"/>
+      <c r="M6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="58"/>
-    </row>
-    <row r="7" spans="1:20" ht="45.75">
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="57"/>
+    </row>
+    <row r="7" spans="1:20" ht="62.25" customHeight="1">
       <c r="A7" s="28"/>
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
@@ -2183,25 +2221,25 @@
       <c r="G7" s="15">
         <v>1</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="36">
         <v>3</v>
       </c>
       <c r="I7" s="31"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="56" t="s">
+      <c r="J7" s="38"/>
+      <c r="K7" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="49"/>
-      <c r="M7" s="57" t="s">
+      <c r="L7" s="48"/>
+      <c r="M7" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="58"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="57"/>
     </row>
     <row r="8" spans="1:20">
       <c r="G8" s="14"/>
@@ -2326,12 +2364,12 @@
       <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
       <c r="L1" s="25" t="s">
         <v>8</v>
       </c>
@@ -2340,13 +2378,13 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="30.75">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
       <c r="H2" s="16" t="s">
         <v>38</v>
       </c>
@@ -2361,38 +2399,38 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
-      <c r="A3" s="69">
+      <c r="A3" s="65">
         <v>6089</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="70">
+      <c r="D3" s="66">
         <v>2639726</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
     </row>
     <row r="4" spans="1:14" ht="184.5" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="72"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="68"/>
       <c r="F4" s="23" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G4" s="17">
         <v>0</v>
@@ -2411,20 +2449,20 @@
       </c>
       <c r="L4" s="26"/>
       <c r="M4" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.6" customHeight="1">
-      <c r="A5" s="69"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="72"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="68"/>
       <c r="F5" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="17">
         <v>6.42</v>
@@ -2443,28 +2481,28 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:14" ht="65.45" customHeight="1">
-      <c r="A7" s="69"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="73"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="17">
         <v>0</v>
@@ -2483,15 +2521,15 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="26.45" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="71" t="s">
-        <v>48</v>
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="67" t="s">
+        <v>49</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" s="20">
         <v>0.05</v>
@@ -2510,11 +2548,11 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="52.5" customHeight="1">
-      <c r="A9" s="69"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="72"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="68"/>
       <c r="F9" s="23" t="s">
         <v>32</v>
       </c>
@@ -2535,28 +2573,28 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="69"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="72"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="68"/>
       <c r="F11" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11" s="15">
         <v>0</v>
@@ -2575,13 +2613,13 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="69"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="73"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="69"/>
       <c r="F12" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="15">
         <v>0</v>
@@ -2596,15 +2634,15 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:14" ht="52.5" customHeight="1">
-      <c r="A13" s="69"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="71" t="s">
-        <v>53</v>
+      <c r="A13" s="65"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="67" t="s">
+        <v>54</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="15">
         <v>5</v>
@@ -2623,115 +2661,115 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="69"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="63">
+      <c r="A16" s="65"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="72">
         <v>0</v>
       </c>
-      <c r="H16" s="63"/>
-      <c r="I16" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" s="63"/>
-      <c r="K16" s="64" t="s">
+      <c r="H16" s="72"/>
+      <c r="I16" s="73" t="s">
         <v>59</v>
       </c>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="69"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="64"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
     </row>
     <row r="18" spans="1:11" ht="65.45" customHeight="1">
-      <c r="A18" s="69"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="71" t="s">
-        <v>60</v>
+      <c r="A18" s="65"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="67" t="s">
+        <v>61</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" s="15">
         <v>0</v>
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="69"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
     </row>
     <row r="20" spans="1:11" ht="26.1">
-      <c r="A20" s="69"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="72"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="68"/>
       <c r="F20" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" s="15">
         <v>0</v>
@@ -2750,13 +2788,13 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="26.1">
-      <c r="A21" s="69"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="72"/>
+      <c r="A21" s="65"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="68"/>
       <c r="F21" s="23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" s="15">
         <v>0</v>
@@ -2775,13 +2813,13 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="104.1">
-      <c r="A22" s="69"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="73"/>
+      <c r="A22" s="65"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="15">
         <v>0</v>
@@ -2790,40 +2828,40 @@
         <v>0.25</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J22" s="21">
         <v>0.75</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="69"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="74" t="s">
+      <c r="A23" s="65"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="F23" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
     </row>
     <row r="24" spans="1:11" ht="26.1">
-      <c r="A24" s="69"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="74"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="70"/>
       <c r="F24" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G24" s="15">
         <v>0</v>
@@ -2842,13 +2880,13 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="26.1">
-      <c r="A25" s="69"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="74"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="70"/>
       <c r="F25" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" s="15">
         <v>0</v>
@@ -2867,13 +2905,13 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="26.1">
-      <c r="A26" s="69"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="74"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="70"/>
       <c r="F26" s="23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G26" s="15">
         <v>0</v>
@@ -2892,26 +2930,26 @@
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="69"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
     </row>
     <row r="28" spans="1:11" ht="26.1">
-      <c r="A28" s="69"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="74"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="70"/>
       <c r="F28" s="23" t="s">
         <v>34</v>
       </c>
@@ -2932,11 +2970,11 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="26.1">
-      <c r="A29" s="69"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="74"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="70"/>
       <c r="F29" s="23" t="s">
         <v>36</v>
       </c>
@@ -2961,25 +2999,25 @@
     </row>
     <row r="31" spans="1:11" ht="26.25" customHeight="1">
       <c r="F31" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:11">
       <c r="F32" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" s="14"/>
     </row>
     <row r="33" spans="6:7">
       <c r="F33" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" s="14"/>
     </row>
     <row r="34" spans="6:7">
       <c r="F34" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" s="14"/>
     </row>
@@ -2988,6 +3026,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="F27:K27"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="F3:K3"/>
     <mergeCell ref="F6:K6"/>
@@ -3004,15 +3051,6 @@
     <mergeCell ref="E18:E22"/>
     <mergeCell ref="E23:E29"/>
     <mergeCell ref="F15:K15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F27:K27"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
@@ -3078,12 +3116,12 @@
       <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="82"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="2" spans="4:9" ht="15" thickBot="1">
       <c r="D2" s="2"/>
@@ -3102,18 +3140,18 @@
       </c>
     </row>
     <row r="3" spans="4:9" ht="27.6" customHeight="1" thickBot="1">
-      <c r="D3" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="79"/>
+      <c r="D3" s="76" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="78"/>
     </row>
     <row r="4" spans="4:9" ht="15.6" thickBot="1">
       <c r="D4" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
@@ -3133,7 +3171,7 @@
     </row>
     <row r="5" spans="4:9" ht="15" thickBot="1">
       <c r="D5" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" s="6">
         <v>6.42</v>
@@ -3152,18 +3190,18 @@
       </c>
     </row>
     <row r="6" spans="4:9" ht="26.1" customHeight="1" thickBot="1">
-      <c r="D6" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="85"/>
+      <c r="D6" s="82" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" spans="4:9" ht="15" thickBot="1">
       <c r="D7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
@@ -3183,7 +3221,7 @@
     </row>
     <row r="8" spans="4:9" ht="15" thickBot="1">
       <c r="D8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="10">
         <v>0.05</v>
@@ -3222,18 +3260,18 @@
       </c>
     </row>
     <row r="10" spans="4:9" ht="15" thickBot="1">
-      <c r="D10" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="79"/>
+      <c r="D10" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="78"/>
     </row>
     <row r="11" spans="4:9" ht="15" thickBot="1">
       <c r="D11" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
@@ -3253,7 +3291,7 @@
     </row>
     <row r="12" spans="4:9" ht="15" thickBot="1">
       <c r="D12" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="5">
         <v>0</v>
@@ -3269,7 +3307,7 @@
     </row>
     <row r="13" spans="4:9" ht="15" thickBot="1">
       <c r="D13" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="5">
         <v>5</v>
@@ -3288,78 +3326,78 @@
       </c>
     </row>
     <row r="14" spans="4:9">
-      <c r="D14" s="86" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="88"/>
+      <c r="D14" s="85" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="87"/>
     </row>
     <row r="15" spans="4:9" ht="15" thickBot="1">
-      <c r="D15" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="91"/>
+      <c r="D15" s="88" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="90"/>
     </row>
     <row r="16" spans="4:9">
-      <c r="D16" s="92" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="94">
+      <c r="D16" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="93">
         <v>0</v>
       </c>
-      <c r="F16" s="96"/>
-      <c r="G16" s="98" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="96"/>
-      <c r="I16" s="75" t="s">
+      <c r="F16" s="95"/>
+      <c r="G16" s="97" t="s">
         <v>83</v>
       </c>
+      <c r="H16" s="95"/>
+      <c r="I16" s="74" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="17" spans="4:9" ht="15" thickBot="1">
-      <c r="D17" s="93"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="97"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="97"/>
-      <c r="I17" s="76"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="75"/>
     </row>
     <row r="18" spans="4:9" ht="15" thickBot="1">
       <c r="D18" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="5">
         <v>0</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="4:9" ht="40.5" customHeight="1" thickBot="1">
-      <c r="D19" s="77" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="79"/>
+      <c r="D19" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="78"/>
     </row>
     <row r="20" spans="4:9" ht="26.45" thickBot="1">
       <c r="D20" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="5">
         <v>0</v>
@@ -3379,7 +3417,7 @@
     </row>
     <row r="21" spans="4:9" ht="26.45" thickBot="1">
       <c r="D21" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" s="5">
         <v>0</v>
@@ -3399,7 +3437,7 @@
     </row>
     <row r="22" spans="4:9" ht="67.5">
       <c r="D22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" s="5">
         <v>0</v>
@@ -3408,28 +3446,28 @@
         <v>0.25</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H22" s="9">
         <v>0.75</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="4:9" ht="40.5" customHeight="1" thickBot="1">
-      <c r="D23" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
+      <c r="D23" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="78"/>
     </row>
     <row r="24" spans="4:9" ht="26.45" thickBot="1">
       <c r="D24" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E24" s="5">
         <v>0</v>
@@ -3449,7 +3487,7 @@
     </row>
     <row r="25" spans="4:9" ht="26.45" thickBot="1">
       <c r="D25" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E25" s="5">
         <v>0</v>
@@ -3469,7 +3507,7 @@
     </row>
     <row r="26" spans="4:9" ht="26.45" thickBot="1">
       <c r="D26" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" s="5">
         <v>0</v>
@@ -3488,14 +3526,14 @@
       </c>
     </row>
     <row r="27" spans="4:9" ht="15" thickBot="1">
-      <c r="D27" s="77" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="79"/>
+      <c r="D27" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="78"/>
     </row>
     <row r="28" spans="4:9" ht="26.45" thickBot="1">
       <c r="D28" s="4" t="s">
@@ -3539,22 +3577,22 @@
     </row>
     <row r="32" spans="4:9">
       <c r="D32" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="4:4">
       <c r="D34" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="4:4">
       <c r="D35" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3599,179 +3637,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="100" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="51" t="s">
-        <v>89</v>
+      <c r="A2" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="51" t="s">
-        <v>90</v>
+      <c r="B3" s="50" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="100" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="51" t="s">
+      <c r="A4" s="101" t="s">
         <v>92</v>
       </c>
+      <c r="B4" s="50" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="100" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="51" t="s">
+      <c r="A5" s="101" t="s">
         <v>94</v>
       </c>
+      <c r="B5" s="50" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="60.75">
-      <c r="A6" s="100" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="51" t="s">
+      <c r="A6" s="101" t="s">
         <v>96</v>
       </c>
+      <c r="B6" s="50" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="100" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="51" t="s">
-        <v>97</v>
+      <c r="A7" s="101" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.75">
-      <c r="A8" s="100" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>98</v>
+      <c r="A8" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30.75">
-      <c r="A9" s="100" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="51" t="s">
+      <c r="A9" s="101" t="s">
         <v>100</v>
       </c>
+      <c r="B9" s="50" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="100" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="101" t="s">
+      <c r="A10" s="101" t="s">
         <v>102</v>
       </c>
+      <c r="B10" s="102" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="101" t="s">
+      <c r="A11" s="101" t="s">
         <v>104</v>
       </c>
+      <c r="B11" s="102" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="30.75">
-      <c r="A12" s="100" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="51" t="s">
+      <c r="A12" s="101" t="s">
         <v>106</v>
       </c>
+      <c r="B12" s="50" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="100" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="101" t="s">
+      <c r="A13" s="101" t="s">
         <v>108</v>
       </c>
+      <c r="B13" s="102" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="100" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="101" t="s">
+      <c r="A14" s="101" t="s">
         <v>110</v>
       </c>
+      <c r="B14" s="102" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" s="101" t="s">
+      <c r="A15" s="101" t="s">
         <v>112</v>
       </c>
+      <c r="B15" s="102" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="101" t="s">
-        <v>113</v>
+      <c r="B16" s="102" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="51" t="s">
-        <v>114</v>
+      <c r="B17" s="50" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="100" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="101" t="s">
+      <c r="A18" s="101" t="s">
         <v>116</v>
       </c>
+      <c r="B18" s="102" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
-      <c r="A19" s="100" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="101" t="s">
+      <c r="A19" s="101" t="s">
         <v>118</v>
       </c>
+      <c r="B19" s="102" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="100" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="101" t="s">
+      <c r="A20" s="101" t="s">
         <v>120</v>
       </c>
+      <c r="B20" s="102" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="102" t="s">
-        <v>121</v>
+      <c r="B21" s="103" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="101" t="s">
-        <v>122</v>
+      <c r="B22" s="102" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3780,15 +3818,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -3799,9 +3828,18 @@
 </p:properties>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3826,6 +3864,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3905,6 +3944,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -4049,13 +4093,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE80185F-2636-40C1-B45C-33FFE5198465}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8739B117-156A-40FE-B2D5-DD22F5B6A59B}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE80185F-2636-40C1-B45C-33FFE5198465}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFF3D39-54DD-416F-A50A-C635A1FF38F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4563AFE2-35FA-493F-8FA9-13CE9E60F181}"/>
 </file>
--- a/01_Input/00_CO Validation/Solomon Islands - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Solomon Islands - Energy Projects.xlsx
@@ -1633,9 +1633,8 @@
       <c r="K2" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="47">
-        <f>((5*15)+(2*30)+(7*13)+(5*30)+(5*10)+(2*30)+(2*15)+(2*50)+26+30+(2*15)+75+25+(3*75)+(2*25)+(16*1.5)+(16*12.5)+2000)/1000</f>
-        <v/>
+      <c r="L2" s="47" t="n">
+        <v>3.301</v>
       </c>
       <c r="M2" s="31" t="inlineStr">
         <is>
@@ -1718,9 +1717,8 @@
         </is>
       </c>
       <c r="K4" s="43" t="n"/>
-      <c r="L4" s="58">
-        <f>0.8*0.25*615804</f>
-        <v/>
+      <c r="L4" s="58" t="n">
+        <v>123160.8</v>
       </c>
       <c r="M4" s="31" t="n"/>
       <c r="N4" s="38" t="n"/>
@@ -1897,7 +1895,7 @@
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="P2:P7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1924,12 +1922,6 @@
     </dataValidation>
     <dataValidation sqref="R2:R7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
